--- a/risk_matrix/risk_matrix_2020.xlsx
+++ b/risk_matrix/risk_matrix_2020.xlsx
@@ -27,11 +27,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -68,10 +68,10 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -516,12 +516,10 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="4" t="n">
         <v>26</v>
       </c>
@@ -538,18 +536,20 @@
           <t>Isolated compromise</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr"/>
+      <c r="B4" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="C4" s="4" t="n">
         <v>3</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>23</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
     </row>
@@ -580,7 +580,9 @@
       <c r="E6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="3" t="inlineStr"/>
+      <c r="F6" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="G6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
@@ -597,10 +599,10 @@
         <v>1</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>3</v>

--- a/risk_matrix/risk_matrix_2020.xlsx
+++ b/risk_matrix/risk_matrix_2020.xlsx
@@ -521,10 +521,10 @@
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="4" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G3" s="4" t="n">
         <v>2</v>

--- a/risk_matrix/risk_matrix_2020.xlsx
+++ b/risk_matrix/risk_matrix_2020.xlsx
@@ -504,7 +504,7 @@
       <c r="C2" s="3" t="inlineStr"/>
       <c r="D2" s="3" t="inlineStr"/>
       <c r="E2" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" s="3" t="inlineStr"/>

--- a/risk_matrix/risk_matrix_2020.xlsx
+++ b/risk_matrix/risk_matrix_2020.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Matrix" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Not placed" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -66,7 +67,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -79,6 +80,9 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +508,7 @@
       <c r="C2" s="3" t="inlineStr"/>
       <c r="D2" s="3" t="inlineStr"/>
       <c r="E2" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" s="3" t="inlineStr"/>
@@ -521,13 +525,13 @@
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="4" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -537,16 +541,16 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>3</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F4" s="4" t="n">
         <v>5</v>
@@ -564,7 +568,9 @@
       <c r="D5" s="3" t="inlineStr"/>
       <c r="E5" s="3" t="inlineStr"/>
       <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
+      <c r="G5" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -574,12 +580,8 @@
       </c>
       <c r="B6" s="3" t="inlineStr"/>
       <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="D6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr"/>
       <c r="F6" s="4" t="n">
         <v>1</v>
       </c>
@@ -592,20 +594,71 @@
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="3" t="inlineStr"/>
+      <c r="D7" s="3" t="inlineStr"/>
+      <c r="E7" s="3" t="inlineStr"/>
+      <c r="F7" s="3" t="inlineStr"/>
+      <c r="G7" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Impact Type</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Stakeholder</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>Classifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Insufficient information</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Insufficient information</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="4" t="n">
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Insufficient information</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Member(s) of the public</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>1</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/risk_matrix/risk_matrix_2020.xlsx
+++ b/risk_matrix/risk_matrix_2020.xlsx
@@ -520,15 +520,15 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3" s="4" t="n">
         <v>1</v>
@@ -550,10 +550,10 @@
         <v>6</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
     </row>
@@ -567,7 +567,9 @@
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr"/>
       <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
+      <c r="F5" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="G5" s="4" t="n">
         <v>1</v>
       </c>
@@ -611,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -661,6 +663,21 @@
         <v>1</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Isolated compromise</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Insufficient information</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
